--- a/write-file/receipt.xlsx
+++ b/write-file/receipt.xlsx
@@ -440,19 +440,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="49" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="5" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,8 +466,6 @@
       <c r="F1" s="1" t="inlineStr"/>
       <c r="G1" s="1" t="inlineStr"/>
       <c r="H1" s="1" t="inlineStr"/>
-      <c r="I1" s="1" t="inlineStr"/>
-      <c r="J1" s="1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -512,8 +508,6 @@
           <t>จำนวนเงิน (รวม VAT)</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -523,18 +517,18 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>8850718810529</t>
+          <t>8850157510493</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>เลย์ร็อคกุ้งเผาซีฟุ๊ด69ก (หน่วย:1ชิ้น)</t>
+          <t>บัตเตอร์กาแฟ 70 กรัม (หน่วย:1ชิ้น)</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>31.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
@@ -545,13 +539,7 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr">
         <is>
-          <t>31.00</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>555</t>
+          <t>12.00</t>
         </is>
       </c>
     </row>
@@ -563,18 +551,18 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>6923655599009</t>
+          <t>8850580100032</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>ดินสอกด 0.5 G990 PK1 (หน่วย:1ชิ้น)</t>
+          <t>โชกี้ช็อกโกแลตแคชชิว 45G(หน่วย:1ชิ้น)</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr"/>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
@@ -585,11 +573,9 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>14.00</t>
-        </is>
-      </c>
-      <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr"/>
+          <t>12.00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -599,18 +585,18 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>8852023664675</t>
+          <t>6923655599009</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>โก๋แก่หิมพานต์อบเกลือ 30ก.(หน่วย:1ชิ้น)</t>
+          <t>ดินสอกด 0.5 G990 PK1 (หน่วย:1ชิ้น)</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="F5" s="1" t="inlineStr">
@@ -621,31 +607,95 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>25.00</t>
-        </is>
-      </c>
-      <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr"/>
+          <t>14.00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ยอดเงินชำระ</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr"/>
-      <c r="C6" s="1" t="inlineStr"/>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>3474370505040</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>เพนเทลไส้ดินสอกตขนาด0.5มม12ไส้ (หน่วย:1ชิ้น)</t>
+        </is>
+      </c>
       <c r="D6" s="1" t="inlineStr"/>
-      <c r="E6" s="1" t="inlineStr"/>
-      <c r="F6" s="1" t="inlineStr"/>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>18.00</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>70.00</t>
-        </is>
-      </c>
-      <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr"/>
+          <t>18.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>8858729210642</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>ปลอกสวม ตราม้า แฟนชี (หน่วย:1ชิ้น)</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>32.00</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr"/>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>32.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>ยอดเงินชำระ</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr"/>
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1" t="inlineStr"/>
+      <c r="F8" s="1" t="inlineStr"/>
+      <c r="G8" s="1" t="inlineStr"/>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>88.00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
